--- a/product_selector_out/STM32N6x5.xlsx
+++ b/product_selector_out/STM32N6x5.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO23"/>
+  <dimension ref="A1:BP23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.56640625" customWidth="1" min="1" max="1"/>
@@ -563,7 +563,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -998,6 +1004,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1332,6 +1339,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -1669,6 +1681,11 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -2006,6 +2023,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -2343,6 +2365,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -2680,6 +2707,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -3017,6 +3049,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -3354,6 +3391,11 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -3691,6 +3733,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -4028,6 +4075,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -4365,6 +4417,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -4702,6 +4759,11 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
@@ -5039,12 +5101,17 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32n645a0.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -5067,12 +5134,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -5087,9 +5156,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -5137,7 +5205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO23"/>
+  <dimension ref="A1:BP23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5207,6 +5275,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5550,6 +5619,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -5647,6 +5721,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -5979,7 +6054,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6316,7 +6396,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6653,7 +6738,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6990,7 +7080,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7327,7 +7422,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7664,7 +7764,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8001,7 +8106,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
+      <c r="BO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8338,7 +8448,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8675,7 +8790,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9012,7 +9132,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9349,7 +9474,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
+      <c r="BO22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9686,7 +9816,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
+      <c r="BO23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9694,8 +9829,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
